--- a/GUA/Waste/B1_Model_Structure.xlsx
+++ b/GUA/Waste/B1_Model_Structure.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E77A823-9192-462C-A35D-A7DA10192B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08ADDD6-7C8B-446C-820E-DD1D8B2B890C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34620" yWindow="2895" windowWidth="17280" windowHeight="8280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sets" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="variables" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sets!$A$1:$L$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sets!$A$1:$L$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="182">
   <si>
     <t>set</t>
   </si>
@@ -377,69 +377,81 @@
     <t>All</t>
   </si>
   <si>
-    <t>CO2e</t>
-  </si>
-  <si>
-    <t>WWWOT</t>
-  </si>
-  <si>
-    <t>WWWT</t>
-  </si>
-  <si>
-    <t>SEWERWW</t>
+    <t>CO2e_WASTE</t>
+  </si>
+  <si>
+    <t>OSS_INORG</t>
+  </si>
+  <si>
+    <t>OSS_ORG</t>
+  </si>
+  <si>
+    <t>NO_OSS</t>
+  </si>
+  <si>
+    <t>NO_COLL_SDF</t>
   </si>
   <si>
     <t>COLL_INORG</t>
   </si>
   <si>
+    <t>COLL_ORG</t>
+  </si>
+  <si>
+    <t>COLL_BLEND</t>
+  </si>
+  <si>
+    <t>NO_COLL</t>
+  </si>
+  <si>
+    <t>INORGSS</t>
+  </si>
+  <si>
+    <t>ORGSS</t>
+  </si>
+  <si>
+    <t>NOSS</t>
+  </si>
+  <si>
+    <t>TSW</t>
+  </si>
+  <si>
+    <t>E5TSWTSW</t>
+  </si>
+  <si>
     <t>INORG_RCY_OS</t>
   </si>
   <si>
-    <t>OSS_INORG</t>
-  </si>
-  <si>
     <t>AD</t>
   </si>
   <si>
-    <t>OSS_ORG</t>
-  </si>
-  <si>
     <t>COMPOST</t>
   </si>
   <si>
-    <t>NO_OSS</t>
-  </si>
-  <si>
     <t>LANDFILL</t>
   </si>
   <si>
-    <t>COLL_ORG</t>
-  </si>
-  <si>
     <t>NO_CONTR_OD</t>
   </si>
   <si>
-    <t>COLL_BLEND</t>
-  </si>
-  <si>
-    <t>INORGSS</t>
-  </si>
-  <si>
-    <t>ORGSS</t>
-  </si>
-  <si>
-    <t>NOSS</t>
-  </si>
-  <si>
-    <t>TSW</t>
-  </si>
-  <si>
-    <t>E5_TSWTSW</t>
+    <t>COPROC</t>
+  </si>
+  <si>
+    <t>INCIN</t>
+  </si>
+  <si>
+    <t>OPEN_BURN</t>
+  </si>
+  <si>
+    <t>SIT_CLAN</t>
   </si>
   <si>
     <t>NO_OSS_BLEND</t>
   </si>
   <si>
+    <t>NO_OSS_NO_COLL</t>
+  </si>
+  <si>
     <t>INORG_DCOLL</t>
   </si>
   <si>
@@ -449,6 +461,9 @@
     <t>BLEND_NO_DCOLL</t>
   </si>
   <si>
+    <t>BLEND_NO_COLL</t>
+  </si>
+  <si>
     <t>INORG_SS</t>
   </si>
   <si>
@@ -461,109 +476,109 @@
     <t>T5TSWTSW</t>
   </si>
   <si>
+    <t>LANDFILL_ELEC</t>
+  </si>
+  <si>
+    <t>E5TSWLANDFILL_ELEC</t>
+  </si>
+  <si>
+    <t>T5LANDFILL_ELECTSW</t>
+  </si>
+  <si>
+    <t>N2O_WASTE</t>
+  </si>
+  <si>
+    <t>CH4_WASTE</t>
+  </si>
+  <si>
+    <t>CO2_WASTE</t>
+  </si>
+  <si>
+    <t>IND_SW</t>
+  </si>
+  <si>
+    <t>E5TSWIND_SW</t>
+  </si>
+  <si>
+    <t>T5IND_SWTSW</t>
+  </si>
+  <si>
+    <t>CO2_CH4_BURN</t>
+  </si>
+  <si>
+    <t>T5CO2_CH4_BURNTSW</t>
+  </si>
+  <si>
+    <t>E5TSWCO2_CH4_BURN</t>
+  </si>
+  <si>
+    <t>GAS_MSW</t>
+  </si>
+  <si>
+    <t>HTC</t>
+  </si>
+  <si>
     <t>GUA</t>
   </si>
   <si>
-    <t>OPEN_BURN</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>AERO_PTAR</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>ANAE_LAGN</t>
-  </si>
-  <si>
-    <t>SEPT_SYST</t>
-  </si>
-  <si>
-    <t>EFLT_DISC</t>
-  </si>
-  <si>
-    <t>LATR</t>
-  </si>
-  <si>
-    <t>DIRECT_DISC</t>
-  </si>
-  <si>
-    <t>MEAT</t>
-  </si>
-  <si>
-    <t>BEER</t>
-  </si>
-  <si>
-    <t>VEGT</t>
-  </si>
-  <si>
-    <t>ANIM</t>
-  </si>
-  <si>
-    <t>SUGR</t>
-  </si>
-  <si>
-    <t>DAIR</t>
-  </si>
-  <si>
-    <t>PETR</t>
-  </si>
-  <si>
-    <t>T5TWWTWW</t>
-  </si>
-  <si>
-    <t>TWW</t>
-  </si>
-  <si>
-    <t>E5_TWWTWW</t>
-  </si>
-  <si>
-    <t>AERO_PTAR_RU</t>
-  </si>
-  <si>
-    <t>ANAE_LAGN_RU</t>
+    <t>DWW_DC</t>
+  </si>
+  <si>
+    <t>DWW_N</t>
+  </si>
+  <si>
+    <t>IWW</t>
+  </si>
+  <si>
+    <t>E5WWDWW_DC</t>
+  </si>
+  <si>
+    <t>E5WWDWW_N</t>
+  </si>
+  <si>
+    <t>E5WWIWW</t>
+  </si>
+  <si>
+    <t>T5DWW_DCWW</t>
+  </si>
+  <si>
+    <t>T5DWW_NWW</t>
+  </si>
+  <si>
+    <t>T5IWWWW</t>
+  </si>
+  <si>
+    <t>COMPOST_DOM</t>
+  </si>
+  <si>
+    <t>COMPOST_COFFEE</t>
+  </si>
+  <si>
+    <t>T5COMPOST_DOMTSW</t>
+  </si>
+  <si>
+    <t>T5COMPOST_COFFEETSW</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_DOM</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_COFFEE</t>
+  </si>
+  <si>
+    <t>salud_residuos</t>
+  </si>
+  <si>
+    <t>contam_agua</t>
+  </si>
+  <si>
+    <t>turismo_residuos</t>
   </si>
   <si>
     <t>RM</t>
   </si>
   <si>
-    <t>SIT_CLAN</t>
-  </si>
-  <si>
-    <t>NO_OSS_NO_COLL</t>
-  </si>
-  <si>
-    <t>BLEND_NO_COLL</t>
-  </si>
-  <si>
-    <t>NO_COLL</t>
-  </si>
-  <si>
-    <t>NO_COLL_SDF</t>
-  </si>
-  <si>
-    <t>LANDFILL_ELEC</t>
-  </si>
-  <si>
     <t>FERT_ORG</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>salud_residuos</t>
-  </si>
-  <si>
-    <t>contam_agua</t>
-  </si>
-  <si>
-    <t>turismo_residuos</t>
   </si>
 </sst>
 </file>
@@ -579,36 +594,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFBDDE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -623,12 +614,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -910,20 +897,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -961,7 +948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -999,7 +986,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1017,11 +1004,11 @@
       </c>
       <c r="E3">
         <f>+COUNTA(E4:E1048576)</f>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <f>+COUNTA(F4:F1048576)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <f t="shared" si="0"/>
@@ -1048,381 +1035,420 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2018</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D4" t="s">
         <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2019</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2020</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2021</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+      <c r="F8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>2023</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="E9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>2024</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+      <c r="F10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2025</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+      <c r="F11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2026</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+      <c r="F12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>2027</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>2028</v>
       </c>
       <c r="C14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" t="s">
         <v>163</v>
       </c>
-      <c r="E14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>2029</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>2030</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>2031</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>2032</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+      <c r="E18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>2033</v>
       </c>
       <c r="C19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" t="s">
         <v>122</v>
       </c>
-      <c r="E19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>2034</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E20" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>2035</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>2036</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="E22" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>2037</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>2038</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>2039</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+      <c r="E25" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>2040</v>
       </c>
       <c r="C26" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>2041</v>
       </c>
       <c r="C27" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>2042</v>
       </c>
       <c r="C28" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>2043</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+      <c r="E29" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>2044</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+      <c r="E30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>2045</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+      <c r="E31" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>2046</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+      <c r="E32" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>2047</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>2048</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>2049</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>2050</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="C37" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="C38" s="1" t="s">
+      <c r="C36" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="C39" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="C40" s="1" t="s">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="C41" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="C42" s="2" t="s">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C42" t="s">
         <v>170</v>
       </c>
     </row>
@@ -1434,39 +1460,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8A1DB5-AB21-4E2D-94E4-FE18AAF65A94}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1796875" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="35.7265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="35.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="40.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="40.7265625" customWidth="1"/>
-    <col min="25" max="25" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.81640625" customWidth="1"/>
+    <col min="20" max="20" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="40.6640625" customWidth="1"/>
+    <col min="25" max="25" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.88671875" customWidth="1"/>
     <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1495,7 +1521,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1590,7 +1616,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1715,7 +1741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -1807,7 +1833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -1893,7 +1919,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>20</v>
       </c>
@@ -1958,7 +1984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
         <v>20</v>
       </c>
@@ -1978,7 +2004,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="L8" t="s">
         <v>20</v>
       </c>
@@ -1998,43 +2024,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A61DBA02-50DA-45DC-88DC-E3B8D7B75762}">
   <dimension ref="A1:AR9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="21" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -2054,7 +2080,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2188,7 +2214,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2365,7 +2391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -2496,7 +2522,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>24</v>
       </c>
@@ -2627,7 +2653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -2740,7 +2766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>20</v>
       </c>
@@ -2796,7 +2822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="H8" t="s">
         <v>20</v>
       </c>
@@ -2822,7 +2848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="M9" t="s">
         <v>20</v>
       </c>
@@ -2836,6 +2862,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
     <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
@@ -3058,37 +3103,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04CF38C1-C2FB-473A-A327-07732310A695}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44268CD1-3016-4647-A333-37075EEAE8F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E67016B-2BB4-478C-AF15-1A9FF8562EBE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B79A15-FCC6-40B1-BEF8-F88BEF3CE214}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0d55314f-45f1-40c9-9fce-63556e193d03"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{721C1776-E710-4064-984A-9AA94D5A5CA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{012BCA27-10E6-496A-8A21-2BE066DB3ED7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>